--- a/site/Slack-Workday-Integration-Guide/headings.xlsx
+++ b/site/Slack-Workday-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -617,7 +617,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Global Settings</t>
+          <t>Integration Scenarios</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -639,86 +639,240 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>General Settings</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KJCV7GW1KWCKZ9HYHB45W3RS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Slack-Workday-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Slack-Workday-Integration-Guide/#h_01KJCV7GW1KWCKZ9HYHB45W3RS</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Integration Settings</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KJA66XMS9JRCHM000N2J4R39</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Slack-Workday-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Slack-Workday-Integration-Guide/#h_01KJA66XMS9JRCHM000N2J4R39</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Workday Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>01KF2STBQHQZSSRVHSD95EW224</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Slack-Workday-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Slack-Workday-Integration-Guide/#01KF2STBQHQZSSRVHSD95EW224</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Log Settings</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>h_01KJCV7GW1MVS3SW7PAR4T4NCD</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Slack-Workday-Integration-Guide/#h_01KJCV7GW1MVS3SW7PAR4T4NCD</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Notification Settings</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Slack-Workday-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Slack-Workday-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Debug Mode</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Slack-Workday-Integration-Guide/#h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Slack-Workday-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Slack-Workday-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Slack-Workday-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Slack-Workday-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>

--- a/site/Slack-Workday-Integration-Guide/headings.xlsx
+++ b/site/Slack-Workday-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -705,29 +705,29 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Slack Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KJCV7GW1MVS3SW7PAR4T4NCD</t>
+          <t>h_01KJF9V3C85QSSPNJ5HRYVHAGS</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Slack-Workday-Integration-Guide/#h_01KJCV7GW1MVS3SW7PAR4T4NCD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Slack-Workday-Integration-Guide/#h_01KJF9V3C85QSSPNJ5HRYVHAGS</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,19 +737,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>h_01KJCV7GW1MVS3SW7PAR4T4NCD</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Slack-Workday-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Slack-Workday-Integration-Guide/#h_01KJCV7GW1MVS3SW7PAR4T4NCD</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,19 +759,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Slack-Workday-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Slack-Workday-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Debug Mode</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,63 +781,63 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Slack-Workday-Integration-Guide/#h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Slack-Workday-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Debug Mode</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Slack-Workday-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Slack-Workday-Integration-Guide/#h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Slack-Workday-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Slack-Workday-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,32 +847,54 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Slack-Workday-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Slack-Workday-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Slack-Workday-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Slack-Workday-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>

--- a/site/Slack-Workday-Integration-Guide/headings.xlsx
+++ b/site/Slack-Workday-Integration-Guide/headings.xlsx
@@ -705,7 +705,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Slack Settings</t>
+          <t>Slack User Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
